--- a/input/timetable/УТС.xlsx
+++ b/input/timetable/УТС.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="124">
   <si>
     <t>пара</t>
   </si>
@@ -335,15 +335,9 @@
     <t>Психология инклюзивного общества (лек 16 ч)</t>
   </si>
   <si>
-    <t>Психология инклюзивного общества (пр), ЭОиДОТ//</t>
-  </si>
-  <si>
     <t>Математические методы искусственного интеллекта (лаб), У105</t>
   </si>
   <si>
-    <t>Математические методы искусственного интеллекта (лаб), У105//</t>
-  </si>
-  <si>
     <t>Параллельное программирование  (лаб), У408</t>
   </si>
   <si>
@@ -359,9 +353,6 @@
     <t>Теория автоматического управления (пр), У504//</t>
   </si>
   <si>
-    <t>Системный подход и системное мышление (лаб), У503</t>
-  </si>
-  <si>
     <t>Программирование на языке Java (лаб), У408</t>
   </si>
   <si>
@@ -393,6 +384,21 @@
   </si>
   <si>
     <t>Русский язык и культура речи (пр), А514//</t>
+  </si>
+  <si>
+    <t>Психология инклюзивного общества (пр), У708// Математические методы искусственного интеллекта (лаб), У105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Психология инклюзивного общества (пр), У708// </t>
+  </si>
+  <si>
+    <t>Операционные системы, п/г 2, У406</t>
+  </si>
+  <si>
+    <t>Операционные системы, п/г 1, У406</t>
+  </si>
+  <si>
+    <t>Системный подход и системное мышление (лаб), У503,605</t>
   </si>
 </sst>
 </file>
@@ -534,7 +540,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="58">
+  <borders count="59">
     <border>
       <left/>
       <right/>
@@ -1242,6 +1248,19 @@
         <color indexed="64"/>
       </right>
       <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
@@ -1257,7 +1276,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="239">
+  <cellXfs count="237">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1724,9 +1743,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1736,12 +1752,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1751,6 +1761,11 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -1784,13 +1799,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2364,7 +2379,7 @@
         <v>4</v>
       </c>
       <c r="C18" s="94" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D18" s="95"/>
       <c r="E18" s="95"/>
@@ -2532,7 +2547,7 @@
         <v>6</v>
       </c>
       <c r="C32" s="139" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D32" s="140"/>
       <c r="E32" s="140"/>
@@ -2625,7 +2640,7 @@
         <v>14</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -3004,7 +3019,7 @@
         <v>3</v>
       </c>
       <c r="C26" s="146" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D26" s="147"/>
       <c r="E26" s="147"/>
@@ -3040,7 +3055,7 @@
         <v>4</v>
       </c>
       <c r="C29" s="130" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D29" s="131"/>
       <c r="E29" s="131"/>
@@ -3052,7 +3067,7 @@
         <v>5</v>
       </c>
       <c r="C30" s="130" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D30" s="131"/>
       <c r="E30" s="131"/>
@@ -3064,7 +3079,7 @@
         <v>6</v>
       </c>
       <c r="C31" s="177" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D31" s="178"/>
       <c r="E31" s="178"/>
@@ -3173,7 +3188,7 @@
         <v>14</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -3314,10 +3329,10 @@
       <c r="A7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="205" t="s">
+      <c r="C7" s="203" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="205"/>
+      <c r="D7" s="203"/>
       <c r="E7" s="15" t="s">
         <v>72</v>
       </c>
@@ -3369,24 +3384,24 @@
       <c r="B11" s="26">
         <v>4</v>
       </c>
-      <c r="C11" s="206" t="s">
+      <c r="C11" s="204" t="s">
         <v>97</v>
       </c>
-      <c r="D11" s="207"/>
-      <c r="E11" s="207"/>
-      <c r="F11" s="208"/>
+      <c r="D11" s="205"/>
+      <c r="E11" s="205"/>
+      <c r="F11" s="206"/>
     </row>
     <row r="12" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="25"/>
       <c r="B12" s="26">
         <v>5</v>
       </c>
-      <c r="C12" s="206" t="s">
+      <c r="C12" s="204" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="207"/>
-      <c r="E12" s="207"/>
-      <c r="F12" s="208"/>
+      <c r="D12" s="205"/>
+      <c r="E12" s="205"/>
+      <c r="F12" s="206"/>
     </row>
     <row r="13" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="28"/>
@@ -3415,12 +3430,12 @@
       <c r="B15" s="26">
         <v>2</v>
       </c>
-      <c r="C15" s="197"/>
-      <c r="D15" s="198"/>
-      <c r="E15" s="198" t="s">
+      <c r="C15" s="194"/>
+      <c r="D15" s="195"/>
+      <c r="E15" s="195" t="s">
         <v>58</v>
       </c>
-      <c r="F15" s="199"/>
+      <c r="F15" s="196"/>
     </row>
     <row r="16" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="25"/>
@@ -3441,22 +3456,26 @@
       <c r="B17" s="26">
         <v>4</v>
       </c>
-      <c r="C17" s="197" t="s">
+      <c r="C17" s="194" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="198"/>
-      <c r="E17" s="200"/>
-      <c r="F17" s="201"/>
-    </row>
-    <row r="18" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D17" s="195"/>
+      <c r="E17" s="195" t="s">
+        <v>121</v>
+      </c>
+      <c r="F17" s="196"/>
+    </row>
+    <row r="18" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="33"/>
       <c r="B18" s="29">
         <v>5</v>
       </c>
-      <c r="C18" s="194"/>
-      <c r="D18" s="195"/>
-      <c r="E18" s="195"/>
-      <c r="F18" s="196"/>
+      <c r="C18" s="94" t="s">
+        <v>122</v>
+      </c>
+      <c r="D18" s="200"/>
+      <c r="E18" s="201"/>
+      <c r="F18" s="202"/>
     </row>
     <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="30" t="s">
@@ -3465,10 +3484,10 @@
       <c r="B19" s="31">
         <v>1</v>
       </c>
-      <c r="C19" s="202"/>
-      <c r="D19" s="203"/>
-      <c r="E19" s="203"/>
-      <c r="F19" s="204"/>
+      <c r="C19" s="197"/>
+      <c r="D19" s="198"/>
+      <c r="E19" s="198"/>
+      <c r="F19" s="199"/>
     </row>
     <row r="20" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="25"/>
@@ -3538,7 +3557,7 @@
         <v>3</v>
       </c>
       <c r="C25" s="130" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D25" s="131"/>
       <c r="E25" s="131"/>
@@ -3550,7 +3569,7 @@
         <v>4</v>
       </c>
       <c r="C26" s="97" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D26" s="98"/>
       <c r="E26" s="98"/>
@@ -3576,7 +3595,7 @@
         <v>4</v>
       </c>
       <c r="C28" s="130" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D28" s="186"/>
       <c r="E28" s="187"/>
@@ -3590,7 +3609,7 @@
       <c r="C29" s="69"/>
       <c r="D29" s="70"/>
       <c r="E29" s="70" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F29" s="71"/>
     </row>
@@ -3611,10 +3630,10 @@
       <c r="B31" s="24">
         <v>1</v>
       </c>
-      <c r="C31" s="202"/>
-      <c r="D31" s="203"/>
-      <c r="E31" s="203"/>
-      <c r="F31" s="204"/>
+      <c r="C31" s="197"/>
+      <c r="D31" s="198"/>
+      <c r="E31" s="198"/>
+      <c r="F31" s="199"/>
     </row>
     <row r="32" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="38"/>
@@ -3622,7 +3641,7 @@
         <v>2</v>
       </c>
       <c r="C32" s="130" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D32" s="131"/>
       <c r="E32" s="131"/>
@@ -3653,22 +3672,22 @@
     <row r="35" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="53"/>
       <c r="B35" s="54"/>
-      <c r="C35" s="209"/>
-      <c r="D35" s="210"/>
-      <c r="E35" s="210"/>
-      <c r="F35" s="211"/>
+      <c r="C35" s="207"/>
+      <c r="D35" s="208"/>
+      <c r="E35" s="208"/>
+      <c r="F35" s="209"/>
     </row>
     <row r="36" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A36" s="51"/>
       <c r="B36" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="212" t="s">
+      <c r="C36" s="210" t="s">
         <v>56</v>
       </c>
-      <c r="D36" s="213"/>
-      <c r="E36" s="213"/>
-      <c r="F36" s="214"/>
+      <c r="D36" s="211"/>
+      <c r="E36" s="211"/>
+      <c r="F36" s="212"/>
     </row>
     <row r="37" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="56" t="s">
@@ -3695,11 +3714,11 @@
         <v>14</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="38">
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C37:F37"/>
@@ -3717,9 +3736,10 @@
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C18:F18"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="C15:D15"/>
@@ -3854,10 +3874,10 @@
       <c r="A7" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="205" t="s">
+      <c r="C7" s="203" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="205"/>
+      <c r="D7" s="203"/>
       <c r="E7" s="15" t="s">
         <v>27</v>
       </c>
@@ -3897,9 +3917,7 @@
       <c r="B10" s="24">
         <v>2</v>
       </c>
-      <c r="C10" s="87" t="s">
-        <v>102</v>
-      </c>
+      <c r="C10" s="87"/>
       <c r="D10" s="88"/>
       <c r="E10" s="88"/>
       <c r="F10" s="89"/>
@@ -3909,10 +3927,10 @@
       <c r="B11" s="26">
         <v>3</v>
       </c>
-      <c r="C11" s="215"/>
-      <c r="D11" s="216"/>
-      <c r="E11" s="216"/>
-      <c r="F11" s="217"/>
+      <c r="C11" s="213"/>
+      <c r="D11" s="214"/>
+      <c r="E11" s="214"/>
+      <c r="F11" s="215"/>
     </row>
     <row r="12" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="25"/>
@@ -3920,7 +3938,7 @@
         <v>4</v>
       </c>
       <c r="C12" s="161" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D12" s="162"/>
       <c r="E12" s="162"/>
@@ -3932,7 +3950,7 @@
         <v>5</v>
       </c>
       <c r="C13" s="161" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D13" s="162"/>
       <c r="E13" s="162"/>
@@ -3968,7 +3986,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="69" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D16" s="70"/>
       <c r="E16" s="70"/>
@@ -3981,7 +3999,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="69" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D17" s="70"/>
       <c r="E17" s="70"/>
@@ -4002,20 +4020,22 @@
         <v>20</v>
       </c>
       <c r="B19" s="31">
-        <v>3</v>
-      </c>
-      <c r="C19" s="218"/>
-      <c r="D19" s="219"/>
-      <c r="E19" s="219"/>
-      <c r="F19" s="220"/>
-    </row>
-    <row r="20" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>4</v>
+      </c>
+      <c r="C19" s="216" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" s="217"/>
+      <c r="E19" s="217"/>
+      <c r="F19" s="218"/>
+    </row>
+    <row r="20" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="25"/>
       <c r="B20" s="26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" s="161" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D20" s="162"/>
       <c r="E20" s="162"/>
@@ -4024,10 +4044,10 @@
     <row r="21" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="33"/>
       <c r="B21" s="29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21" s="94" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D21" s="95"/>
       <c r="E21" s="95"/>
@@ -4061,7 +4081,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="69" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D24" s="70"/>
       <c r="E24" s="70"/>
@@ -4084,22 +4104,22 @@
       <c r="B26" s="31">
         <v>2</v>
       </c>
-      <c r="C26" s="230"/>
-      <c r="D26" s="231"/>
-      <c r="E26" s="231"/>
-      <c r="F26" s="232"/>
+      <c r="C26" s="228"/>
+      <c r="D26" s="229"/>
+      <c r="E26" s="229"/>
+      <c r="F26" s="230"/>
     </row>
     <row r="27" spans="1:6" ht="17.45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="34"/>
       <c r="B27" s="24">
         <v>3</v>
       </c>
-      <c r="C27" s="233" t="s">
+      <c r="C27" s="231" t="s">
         <v>36</v>
       </c>
-      <c r="D27" s="234"/>
-      <c r="E27" s="234"/>
-      <c r="F27" s="235"/>
+      <c r="D27" s="232"/>
+      <c r="E27" s="232"/>
+      <c r="F27" s="233"/>
     </row>
     <row r="28" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="34"/>
@@ -4118,42 +4138,42 @@
       <c r="B29" s="29">
         <v>5</v>
       </c>
-      <c r="C29" s="236"/>
-      <c r="D29" s="237"/>
-      <c r="E29" s="237"/>
-      <c r="F29" s="238"/>
+      <c r="C29" s="234"/>
+      <c r="D29" s="235"/>
+      <c r="E29" s="235"/>
+      <c r="F29" s="236"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" s="37" t="s">
         <v>23</v>
       </c>
       <c r="B30" s="24"/>
-      <c r="C30" s="224" t="s">
+      <c r="C30" s="222" t="s">
         <v>59</v>
       </c>
-      <c r="D30" s="225"/>
-      <c r="E30" s="225"/>
-      <c r="F30" s="226"/>
+      <c r="D30" s="223"/>
+      <c r="E30" s="223"/>
+      <c r="F30" s="224"/>
     </row>
     <row r="31" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="35"/>
       <c r="B31" s="66"/>
-      <c r="C31" s="227"/>
-      <c r="D31" s="228"/>
-      <c r="E31" s="228"/>
-      <c r="F31" s="229"/>
+      <c r="C31" s="225"/>
+      <c r="D31" s="226"/>
+      <c r="E31" s="226"/>
+      <c r="F31" s="227"/>
     </row>
     <row r="32" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A32" s="67"/>
       <c r="B32" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="C32" s="221" t="s">
+      <c r="C32" s="219" t="s">
         <v>101</v>
       </c>
-      <c r="D32" s="222"/>
-      <c r="E32" s="222"/>
-      <c r="F32" s="223"/>
+      <c r="D32" s="220"/>
+      <c r="E32" s="220"/>
+      <c r="F32" s="221"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33" s="2" t="s">
@@ -4168,7 +4188,7 @@
         <v>14</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/input/timetable/УТС.xlsx
+++ b/input/timetable/УТС.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14715" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14715"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="168">
   <si>
     <t>пара</t>
   </si>
@@ -74,6 +74,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -119,33 +122,72 @@
     <t>весенний</t>
   </si>
   <si>
+    <t>Веселов С.И.</t>
+  </si>
+  <si>
+    <t>Дубовик А.О.</t>
+  </si>
+  <si>
     <t>Физическая культура и спорт (лек 8 ч)</t>
   </si>
   <si>
+    <t>Гришмановский П.В.</t>
+  </si>
+  <si>
+    <t>Кузин Д.А.</t>
+  </si>
+  <si>
     <t>Структурное программирование (лек), У903</t>
   </si>
   <si>
     <t>Математический анализ (лек). У903</t>
   </si>
   <si>
+    <t>Паук Е.Н.</t>
+  </si>
+  <si>
+    <t>Запевалова Л.Ю.</t>
+  </si>
+  <si>
     <t>Цифровая схемотехника (лек), У903</t>
   </si>
   <si>
     <t>Программируемые логические контроллеры (лек), У903</t>
   </si>
   <si>
+    <t>Запевалов А.В.</t>
+  </si>
+  <si>
     <t>Теория автоматического управления (лек), У503</t>
   </si>
   <si>
+    <t>Тараканов Д.В.</t>
+  </si>
+  <si>
+    <t>Даниленко И.Н.</t>
+  </si>
+  <si>
     <t>Математические методы искусственного интеллекта (лек), У903</t>
   </si>
   <si>
+    <t>Карамышев Э.Р.</t>
+  </si>
+  <si>
+    <t>Назин А.Г.</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Компьютерная графика (лек), У903//</t>
   </si>
   <si>
+    <t>Кошкин А.С.</t>
+  </si>
+  <si>
     <t>Структуры и алгоритмы обработки данных (лек). У903</t>
   </si>
   <si>
+    <t>Брыкин В.В.</t>
+  </si>
+  <si>
     <t>Математические методы искусственного интеллекта (лек),У903</t>
   </si>
   <si>
@@ -179,9 +221,15 @@
     <t>История России (лек 32 ч)</t>
   </si>
   <si>
+    <t>Шадрин Г.А.</t>
+  </si>
+  <si>
     <t>Структурное программирование,  п/г 1, У408</t>
   </si>
   <si>
+    <t>Луппов Е.А.</t>
+  </si>
+  <si>
     <t>Структурное программирование,п/г 2, У408</t>
   </si>
   <si>
@@ -194,18 +242,33 @@
     <t>Элективные дисциплины по физической культуре и спорту проводятся  4 парой или  5 парой в зависимости от выбранной элективной дисциплины</t>
   </si>
   <si>
+    <t>Иксанова И.Р.</t>
+  </si>
+  <si>
     <t>Базы данных, п/г 2, У504</t>
   </si>
   <si>
     <t>Основы предпринимательской деятельности (лек 16ч)</t>
   </si>
   <si>
+    <t>Смирнова И.В.</t>
+  </si>
+  <si>
+    <t>Назаров Е.В.</t>
+  </si>
+  <si>
     <t>Распознавание образов и обр. изображений, п/г 1, У105</t>
   </si>
   <si>
     <t>Распознавание образов и обр. изображений, п/г 2, У105</t>
   </si>
   <si>
+    <t>Чуланова О.Л.</t>
+  </si>
+  <si>
+    <t>Кислова Н.А.</t>
+  </si>
+  <si>
     <t>День самостоятельной работы</t>
   </si>
   <si>
@@ -230,6 +293,9 @@
     <t xml:space="preserve">                    РАСПИСАНИЕ УЧЕБНЫХ ЗАНЯТИЙ </t>
   </si>
   <si>
+    <t>Гребенюк Е.В.</t>
+  </si>
+  <si>
     <t>"____"_______2026 г.</t>
   </si>
   <si>
@@ -254,6 +320,27 @@
     <t>Инженерия автоматизированных, информационных и робототехнических систем                      ТО:02.02.2026-28.03.2026</t>
   </si>
   <si>
+    <t>Щипицин К.П.</t>
+  </si>
+  <si>
+    <t>Сташкин П.Р.</t>
+  </si>
+  <si>
+    <t>Гришенкова Т.Ф.</t>
+  </si>
+  <si>
+    <t>Чеснокова Н.Е.</t>
+  </si>
+  <si>
+    <t>Чеснокова Н.Е.; Гришмановская О.Н, Гришмановский П.В.</t>
+  </si>
+  <si>
+    <t>Ненахова Н.А.</t>
+  </si>
+  <si>
+    <t>Гришмановская О.Н, Гришмановский П.В.;Алиев М.У.</t>
+  </si>
+  <si>
     <t>Физика (лек), У903</t>
   </si>
   <si>
@@ -290,6 +377,12 @@
     <t>Программирование на языке Java (лек),ЭОиДОТ</t>
   </si>
   <si>
+    <t>Алиев М.У.;</t>
+  </si>
+  <si>
+    <t>Запевалова Л.Ю.; Подлуцкая К.А.</t>
+  </si>
+  <si>
     <t>// Цифровая схемотехника (пр), У503</t>
   </si>
   <si>
@@ -302,6 +395,9 @@
     <t>Компьютерная графика (лаб), ЭОиДОТ//</t>
   </si>
   <si>
+    <t>Смирнова И.В./Запевалов А.В.</t>
+  </si>
+  <si>
     <t>Основы предпринимательской деятельности (пр). А414// Робототехника (лек), У503</t>
   </si>
   <si>
@@ -311,18 +407,33 @@
     <t>Дифференциальные уравнения (пр), У506</t>
   </si>
   <si>
+    <t>Назаров Е.В.; Евласьев А.П.</t>
+  </si>
+  <si>
+    <t>Евласьев А.П..; Назаров Е.В.</t>
+  </si>
+  <si>
     <t>// Физика (пр), А304</t>
   </si>
   <si>
+    <t>Паук Е.Н/.Запевалова Л.Ю.</t>
+  </si>
+  <si>
     <t>Системный подход и системное мышление (лек), У903// Инженерная графика (лек), У903</t>
   </si>
   <si>
     <t>Операционные системы (лек), У903</t>
   </si>
   <si>
+    <t>Золотарева Н.С.</t>
+  </si>
+  <si>
     <t>Устройства автоматизированных систем (лек), У503// Распознавание образов и обработка изображений (лек), У503</t>
   </si>
   <si>
+    <t>Назаров Е.В./Тараканов Д.В.</t>
+  </si>
+  <si>
     <t>Основы предпринимательской деятельности (пр), А410</t>
   </si>
   <si>
@@ -335,6 +446,9 @@
     <t>Психология инклюзивного общества (лек 16 ч)</t>
   </si>
   <si>
+    <t>Самойлова М.В.</t>
+  </si>
+  <si>
     <t>Математические методы искусственного интеллекта (лаб), У105</t>
   </si>
   <si>
@@ -350,6 +464,9 @@
     <t>Иностранный язык в профессиональной сфере (пр), А503</t>
   </si>
   <si>
+    <t>Гришмановская О.Н.</t>
+  </si>
+  <si>
     <t>Теория автоматического управления (пр), У504//</t>
   </si>
   <si>
@@ -362,6 +479,9 @@
     <t>ФТД: Основы имиджевой коммуникации (лек), К202//</t>
   </si>
   <si>
+    <t>Брыкин В.В.; Запевалов А.В.</t>
+  </si>
+  <si>
     <t>Мехатронные комплексы (лек), У903</t>
   </si>
   <si>
@@ -389,13 +509,25 @@
     <t>Психология инклюзивного общества (пр), У708// Математические методы искусственного интеллекта (лаб), У105</t>
   </si>
   <si>
+    <t>Батыршина К.В./Брыкин В.В.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Психология инклюзивного общества (пр), У708// </t>
   </si>
   <si>
+    <t>Батыршина К.Г.</t>
+  </si>
+  <si>
     <t>Операционные системы, п/г 2, У406</t>
   </si>
   <si>
     <t>Операционные системы, п/г 1, У406</t>
+  </si>
+  <si>
+    <t>Запевалов А.В.; Кривицкая М.А.</t>
+  </si>
+  <si>
+    <t>Кривицкая М.А.</t>
   </si>
   <si>
     <t>Системный подход и системное мышление (лаб), У503,605</t>
@@ -510,7 +642,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -529,6 +661,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -540,7 +678,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="59">
+  <borders count="63">
     <border>
       <left/>
       <right/>
@@ -661,6 +799,49 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1223,6 +1404,19 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1276,7 +1470,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="237">
+  <cellXfs count="258">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1316,28 +1510,31 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1346,7 +1543,8 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1370,59 +1568,66 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1433,74 +1638,55 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1508,116 +1694,207 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1626,223 +1903,163 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2152,7 +2369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2161,10 +2378,11 @@
     <col min="4" max="4" width="17.85546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="19" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -2172,15 +2390,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -2188,39 +2406,39 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -2230,35 +2448,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="105"/>
+      <c r="D7" s="119"/>
       <c r="E7" s="15" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="117" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="117"/>
-      <c r="E8" s="117"/>
-      <c r="F8" s="117"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="C8" s="131" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="131"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="131"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>0</v>
@@ -2269,402 +2487,462 @@
       <c r="D9" s="20"/>
       <c r="E9" s="21"/>
       <c r="F9" s="22"/>
-    </row>
-    <row r="10" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="24">
+      <c r="G9" s="23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="25">
         <v>1</v>
       </c>
-      <c r="C10" s="109" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" s="110"/>
-      <c r="E10" s="110"/>
-      <c r="F10" s="111"/>
-    </row>
-    <row r="11" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="25"/>
-      <c r="B11" s="26">
+      <c r="C10" s="123" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="124"/>
+      <c r="E10" s="124"/>
+      <c r="F10" s="125"/>
+      <c r="G10" s="76" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="26"/>
+      <c r="B11" s="27">
         <v>2</v>
       </c>
-      <c r="C11" s="106" t="s">
+      <c r="C11" s="120" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="122"/>
+      <c r="G11" s="74" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
+        <v>3</v>
+      </c>
+      <c r="C12" s="120" t="s">
+        <v>104</v>
+      </c>
+      <c r="D12" s="121"/>
+      <c r="E12" s="121"/>
+      <c r="F12" s="122"/>
+      <c r="G12" s="74" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27">
+        <v>4</v>
+      </c>
+      <c r="C13" s="120" t="s">
+        <v>128</v>
+      </c>
+      <c r="D13" s="121"/>
+      <c r="E13" s="121"/>
+      <c r="F13" s="122"/>
+      <c r="G13" s="74" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="30"/>
+      <c r="B14" s="31">
+        <v>5</v>
+      </c>
+      <c r="C14" s="126"/>
+      <c r="D14" s="127"/>
+      <c r="E14" s="127"/>
+      <c r="F14" s="128"/>
+      <c r="G14" s="79"/>
+    </row>
+    <row r="15" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="33">
+        <v>1</v>
+      </c>
+      <c r="C15" s="117" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" s="118"/>
+      <c r="E15" s="129" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="130"/>
+      <c r="G15" s="76" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
+        <v>2</v>
+      </c>
+      <c r="C16" s="114" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="115"/>
+      <c r="E16" s="115" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="116"/>
+      <c r="G16" s="74" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
+        <v>3</v>
+      </c>
+      <c r="C17" s="132" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" s="133"/>
+      <c r="E17" s="133"/>
+      <c r="F17" s="134"/>
+      <c r="G17" s="74" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" s="34"/>
+    </row>
+    <row r="18" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="35"/>
+      <c r="B18" s="31">
+        <v>4</v>
+      </c>
+      <c r="C18" s="154" t="s">
+        <v>158</v>
+      </c>
+      <c r="D18" s="155"/>
+      <c r="E18" s="155"/>
+      <c r="F18" s="156"/>
+      <c r="G18" s="79" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="33">
+        <v>1</v>
+      </c>
+      <c r="C19" s="138"/>
+      <c r="D19" s="139"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="140"/>
+      <c r="G19" s="76"/>
+    </row>
+    <row r="20" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27">
+        <v>2</v>
+      </c>
+      <c r="C20" s="150" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="151"/>
+      <c r="E20" s="152"/>
+      <c r="F20" s="153"/>
+      <c r="G20" s="74" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
+        <v>3</v>
+      </c>
+      <c r="C21" s="160" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="161"/>
+      <c r="E21" s="161"/>
+      <c r="F21" s="162"/>
+      <c r="G21" s="74" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="35"/>
+      <c r="B22" s="31">
+        <v>4</v>
+      </c>
+      <c r="C22" s="157" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="158"/>
+      <c r="E22" s="158"/>
+      <c r="F22" s="159"/>
+      <c r="G22" s="74" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A23" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="33">
+        <v>1</v>
+      </c>
+      <c r="C23" s="147"/>
+      <c r="D23" s="148"/>
+      <c r="E23" s="148" t="s">
+        <v>108</v>
+      </c>
+      <c r="F23" s="149"/>
+      <c r="G23" s="76" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27">
+        <v>2</v>
+      </c>
+      <c r="C24" s="160" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="161"/>
+      <c r="E24" s="161" t="s">
+        <v>111</v>
+      </c>
+      <c r="F24" s="162"/>
+      <c r="G24" s="77" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27">
+        <v>3</v>
+      </c>
+      <c r="C25" s="160" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="161"/>
+      <c r="E25" s="161"/>
+      <c r="F25" s="162"/>
+      <c r="G25" s="74" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A26" s="60"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="144"/>
+      <c r="D26" s="145"/>
+      <c r="E26" s="145"/>
+      <c r="F26" s="146"/>
+      <c r="G26" s="28"/>
+    </row>
+    <row r="27" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="35"/>
+      <c r="B27" s="31">
+        <v>7</v>
+      </c>
+      <c r="C27" s="141" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="142"/>
+      <c r="E27" s="142"/>
+      <c r="F27" s="143"/>
+      <c r="G27" s="79" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A28" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="33">
+        <v>2</v>
+      </c>
+      <c r="C28" s="135"/>
+      <c r="D28" s="136"/>
+      <c r="E28" s="136"/>
+      <c r="F28" s="137"/>
+      <c r="G28" s="45"/>
+    </row>
+    <row r="29" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="36"/>
+      <c r="B29" s="27">
+        <v>3</v>
+      </c>
+      <c r="C29" s="144"/>
+      <c r="D29" s="145"/>
+      <c r="E29" s="145"/>
+      <c r="F29" s="146"/>
+      <c r="G29" s="28"/>
+    </row>
+    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="37"/>
+      <c r="B30" s="29">
+        <v>4</v>
+      </c>
+      <c r="C30" s="160" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="161"/>
+      <c r="E30" s="161" t="s">
+        <v>55</v>
+      </c>
+      <c r="F30" s="162"/>
+      <c r="G30" s="74" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="37"/>
+      <c r="B31" s="29">
+        <v>5</v>
+      </c>
+      <c r="C31" s="102" t="s">
+        <v>130</v>
+      </c>
+      <c r="D31" s="103"/>
+      <c r="E31" s="103"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="74" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="38"/>
+      <c r="B32" s="31">
+        <v>6</v>
+      </c>
+      <c r="C32" s="111" t="s">
+        <v>167</v>
+      </c>
+      <c r="D32" s="112"/>
+      <c r="E32" s="112"/>
+      <c r="F32" s="113"/>
+      <c r="G32" s="74" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B33" s="33">
+        <v>2</v>
+      </c>
+      <c r="C33" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33" s="100"/>
+      <c r="E33" s="100"/>
+      <c r="F33" s="101"/>
+      <c r="G33" s="76" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="40"/>
+      <c r="B34" s="27">
+        <v>4</v>
+      </c>
+      <c r="C34" s="102"/>
+      <c r="D34" s="103"/>
+      <c r="E34" s="103"/>
+      <c r="F34" s="104"/>
+      <c r="G34" s="74"/>
+    </row>
+    <row r="35" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="50"/>
+      <c r="B35" s="31">
+        <v>5</v>
+      </c>
+      <c r="C35" s="96"/>
+      <c r="D35" s="97"/>
+      <c r="E35" s="97"/>
+      <c r="F35" s="98"/>
+      <c r="G35" s="28"/>
+    </row>
+    <row r="36" spans="1:7" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="66"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="93"/>
+      <c r="D36" s="94"/>
+      <c r="E36" s="94"/>
+      <c r="F36" s="95"/>
+      <c r="G36" s="68"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="42"/>
+      <c r="B37" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="108" t="s">
+        <v>63</v>
+      </c>
+      <c r="D37" s="109"/>
+      <c r="E37" s="109"/>
+      <c r="F37" s="110"/>
+      <c r="G37" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="107"/>
-      <c r="E11" s="107"/>
-      <c r="F11" s="108"/>
-    </row>
-    <row r="12" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
-        <v>3</v>
-      </c>
-      <c r="C12" s="106" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" s="107"/>
-      <c r="E12" s="107"/>
-      <c r="F12" s="108"/>
-    </row>
-    <row r="13" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
-        <v>4</v>
-      </c>
-      <c r="C13" s="106" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" s="107"/>
-      <c r="E13" s="107"/>
-      <c r="F13" s="108"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="28"/>
-      <c r="B14" s="29">
-        <v>5</v>
-      </c>
-      <c r="C14" s="112"/>
-      <c r="D14" s="113"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="114"/>
-    </row>
-    <row r="15" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="31">
-        <v>1</v>
-      </c>
-      <c r="C15" s="103" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" s="104"/>
-      <c r="E15" s="115" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" s="116"/>
-    </row>
-    <row r="16" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
-        <v>2</v>
-      </c>
-      <c r="C16" s="100" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="101"/>
-      <c r="E16" s="101" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" s="102"/>
-    </row>
-    <row r="17" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
-        <v>3</v>
-      </c>
-      <c r="C17" s="75" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="76"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="32"/>
-    </row>
-    <row r="18" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="33"/>
-      <c r="B18" s="29">
-        <v>4</v>
-      </c>
-      <c r="C18" s="94" t="s">
-        <v>118</v>
-      </c>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="96"/>
-    </row>
-    <row r="19" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="31">
-        <v>1</v>
-      </c>
-      <c r="C19" s="81"/>
-      <c r="D19" s="82"/>
-      <c r="E19" s="82"/>
-      <c r="F19" s="83"/>
-    </row>
-    <row r="20" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26">
-        <v>2</v>
-      </c>
-      <c r="C20" s="90" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" s="91"/>
-      <c r="E20" s="92"/>
-      <c r="F20" s="93"/>
-    </row>
-    <row r="21" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26">
-        <v>3</v>
-      </c>
-      <c r="C21" s="69" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="71"/>
-    </row>
-    <row r="22" spans="1:7" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="33"/>
-      <c r="B22" s="29">
-        <v>4</v>
-      </c>
-      <c r="C22" s="97" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22" s="98"/>
-      <c r="E22" s="98"/>
-      <c r="F22" s="99"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A23" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="31">
-        <v>1</v>
-      </c>
-      <c r="C23" s="87"/>
-      <c r="D23" s="88"/>
-      <c r="E23" s="88" t="s">
-        <v>79</v>
-      </c>
-      <c r="F23" s="89"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26">
-        <v>2</v>
-      </c>
-      <c r="C24" s="69" t="s">
-        <v>78</v>
-      </c>
-      <c r="D24" s="70"/>
-      <c r="E24" s="70" t="s">
-        <v>82</v>
-      </c>
-      <c r="F24" s="71"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26">
-        <v>3</v>
-      </c>
-      <c r="C25" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" s="70"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="71"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A26" s="55"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="72"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="74"/>
-    </row>
-    <row r="27" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="33"/>
-      <c r="B27" s="29">
-        <v>7</v>
-      </c>
-      <c r="C27" s="84" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27" s="85"/>
-      <c r="E27" s="85"/>
-      <c r="F27" s="86"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A28" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="31">
-        <v>2</v>
-      </c>
-      <c r="C28" s="78"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="79"/>
-      <c r="F28" s="80"/>
-    </row>
-    <row r="29" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="34"/>
-      <c r="B29" s="26">
-        <v>3</v>
-      </c>
-      <c r="C29" s="72"/>
-      <c r="D29" s="73"/>
-      <c r="E29" s="73"/>
-      <c r="F29" s="74"/>
-    </row>
-    <row r="30" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="35"/>
-      <c r="B30" s="27">
-        <v>4</v>
-      </c>
-      <c r="C30" s="69" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" s="70"/>
-      <c r="E30" s="70" t="s">
-        <v>41</v>
-      </c>
-      <c r="F30" s="71"/>
-    </row>
-    <row r="31" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="35"/>
-      <c r="B31" s="27">
-        <v>5</v>
-      </c>
-      <c r="C31" s="130" t="s">
-        <v>95</v>
-      </c>
-      <c r="D31" s="131"/>
-      <c r="E31" s="131"/>
-      <c r="F31" s="132"/>
-    </row>
-    <row r="32" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="36"/>
-      <c r="B32" s="29">
-        <v>6</v>
-      </c>
-      <c r="C32" s="139" t="s">
-        <v>123</v>
-      </c>
-      <c r="D32" s="140"/>
-      <c r="E32" s="140"/>
-      <c r="F32" s="141"/>
-    </row>
-    <row r="33" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="B33" s="31">
-        <v>2</v>
-      </c>
-      <c r="C33" s="127" t="s">
-        <v>26</v>
-      </c>
-      <c r="D33" s="128"/>
-      <c r="E33" s="128"/>
-      <c r="F33" s="129"/>
-    </row>
-    <row r="34" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="38"/>
-      <c r="B34" s="26">
-        <v>4</v>
-      </c>
-      <c r="C34" s="130"/>
-      <c r="D34" s="131"/>
-      <c r="E34" s="131"/>
-      <c r="F34" s="132"/>
-    </row>
-    <row r="35" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="46"/>
-      <c r="B35" s="29">
-        <v>5</v>
-      </c>
-      <c r="C35" s="124"/>
-      <c r="D35" s="125"/>
-      <c r="E35" s="125"/>
-      <c r="F35" s="126"/>
-    </row>
-    <row r="36" spans="1:6" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="58"/>
-      <c r="B36" s="59"/>
-      <c r="C36" s="121"/>
-      <c r="D36" s="122"/>
-      <c r="E36" s="122"/>
-      <c r="F36" s="123"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="40"/>
-      <c r="B37" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="C37" s="136" t="s">
-        <v>49</v>
-      </c>
-      <c r="D37" s="137"/>
-      <c r="E37" s="137"/>
-      <c r="F37" s="138"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A38" s="38"/>
-      <c r="B38" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="C38" s="133" t="s">
-        <v>30</v>
-      </c>
-      <c r="D38" s="134"/>
-      <c r="E38" s="134"/>
-      <c r="F38" s="135"/>
-    </row>
-    <row r="39" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="46"/>
-      <c r="B39" s="64"/>
-      <c r="C39" s="118"/>
-      <c r="D39" s="119"/>
-      <c r="E39" s="119"/>
-      <c r="F39" s="120"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38" s="40"/>
+      <c r="B38" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="105" t="s">
+        <v>33</v>
+      </c>
+      <c r="D38" s="106"/>
+      <c r="E38" s="106"/>
+      <c r="F38" s="107"/>
+      <c r="G38" s="75" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="50"/>
+      <c r="B39" s="80"/>
+      <c r="C39" s="90"/>
+      <c r="D39" s="91"/>
+      <c r="E39" s="91"/>
+      <c r="F39" s="92"/>
+      <c r="G39" s="81"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>117</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="C39:F39"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C25:F25"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C19:F19"/>
@@ -2678,11 +2956,26 @@
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="E24:F24"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C32:F32"/>
   </mergeCells>
   <conditionalFormatting sqref="C8">
     <cfRule type="expression" priority="2">
@@ -2705,7 +2998,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2713,10 +3006,11 @@
     <col min="3" max="3" width="18.7109375" style="2" customWidth="1"/>
     <col min="4" max="5" width="16.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -2724,15 +3018,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -2740,39 +3034,39 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -2782,35 +3076,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="105"/>
+      <c r="D7" s="119"/>
       <c r="E7" s="15" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="117" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="117"/>
-      <c r="E8" s="117"/>
-      <c r="F8" s="117"/>
-    </row>
-    <row r="9" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="C8" s="131" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" s="131"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="131"/>
+    </row>
+    <row r="9" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>0</v>
@@ -2821,378 +3115,465 @@
       <c r="D9" s="20"/>
       <c r="E9" s="21"/>
       <c r="F9" s="22"/>
-    </row>
-    <row r="10" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="31">
+      <c r="G9" s="23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="33">
         <v>1</v>
       </c>
-      <c r="C10" s="145" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" s="115"/>
-      <c r="E10" s="115"/>
-      <c r="F10" s="116"/>
-    </row>
-    <row r="11" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="25"/>
-      <c r="B11" s="26">
+      <c r="C10" s="176" t="s">
+        <v>124</v>
+      </c>
+      <c r="D10" s="129"/>
+      <c r="E10" s="129"/>
+      <c r="F10" s="130"/>
+      <c r="G10" s="76" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="26"/>
+      <c r="B11" s="27">
         <v>2</v>
       </c>
-      <c r="C11" s="146" t="s">
-        <v>93</v>
-      </c>
-      <c r="D11" s="147"/>
-      <c r="E11" s="147"/>
-      <c r="F11" s="148"/>
-    </row>
-    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="C11" s="170" t="s">
+        <v>125</v>
+      </c>
+      <c r="D11" s="171"/>
+      <c r="E11" s="171"/>
+      <c r="F11" s="172"/>
+      <c r="G11" s="74" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
         <v>3</v>
       </c>
-      <c r="C12" s="142"/>
-      <c r="D12" s="143"/>
-      <c r="E12" s="143"/>
-      <c r="F12" s="144"/>
-    </row>
-    <row r="13" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="65"/>
-      <c r="B13" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="149" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="150"/>
-      <c r="E13" s="150"/>
-      <c r="F13" s="151"/>
-    </row>
-    <row r="14" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="31">
+      <c r="C12" s="198"/>
+      <c r="D12" s="199"/>
+      <c r="E12" s="199"/>
+      <c r="F12" s="200"/>
+      <c r="G12" s="28"/>
+    </row>
+    <row r="13" spans="1:12" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="83"/>
+      <c r="B13" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="201" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="202"/>
+      <c r="E13" s="202"/>
+      <c r="F13" s="203"/>
+      <c r="G13" s="61"/>
+    </row>
+    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="33">
         <v>1</v>
       </c>
-      <c r="C14" s="81"/>
-      <c r="D14" s="82"/>
-      <c r="E14" s="82"/>
-      <c r="F14" s="83"/>
-    </row>
-    <row r="15" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="25"/>
-      <c r="B15" s="24">
+      <c r="C14" s="138"/>
+      <c r="D14" s="139"/>
+      <c r="E14" s="139"/>
+      <c r="F14" s="140"/>
+      <c r="G14" s="76"/>
+    </row>
+    <row r="15" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="26"/>
+      <c r="B15" s="25">
         <v>2</v>
       </c>
-      <c r="C15" s="161" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" s="162"/>
-      <c r="E15" s="162"/>
-      <c r="F15" s="163"/>
-      <c r="K15" s="44"/>
-    </row>
-    <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
+      <c r="C15" s="167" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" s="168"/>
+      <c r="E15" s="168"/>
+      <c r="F15" s="169"/>
+      <c r="G15" s="74" t="s">
+        <v>39</v>
+      </c>
+      <c r="L15" s="48"/>
+    </row>
+    <row r="16" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
         <v>3</v>
       </c>
-      <c r="C16" s="130" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16" s="131"/>
-      <c r="E16" s="131"/>
-      <c r="F16" s="132"/>
-    </row>
-    <row r="17" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
+      <c r="C16" s="102" t="s">
+        <v>113</v>
+      </c>
+      <c r="D16" s="103"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="104"/>
+      <c r="G16" s="74" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
         <v>4</v>
       </c>
-      <c r="C17" s="146" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" s="147"/>
-      <c r="E17" s="147"/>
-      <c r="F17" s="148"/>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="33"/>
-      <c r="B18" s="29">
+      <c r="C17" s="170" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17" s="171"/>
+      <c r="E17" s="171"/>
+      <c r="F17" s="172"/>
+      <c r="G17" s="74" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="35"/>
+      <c r="B18" s="31">
         <v>5</v>
       </c>
-      <c r="C18" s="167"/>
-      <c r="D18" s="168"/>
-      <c r="E18" s="168"/>
-      <c r="F18" s="169"/>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="31">
+      <c r="C18" s="195"/>
+      <c r="D18" s="196"/>
+      <c r="E18" s="196"/>
+      <c r="F18" s="197"/>
+      <c r="G18" s="79"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="33">
         <v>1</v>
       </c>
-      <c r="C19" s="164"/>
-      <c r="D19" s="165"/>
-      <c r="E19" s="165"/>
-      <c r="F19" s="166"/>
-    </row>
-    <row r="20" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26">
+      <c r="C19" s="192"/>
+      <c r="D19" s="193"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="194"/>
+      <c r="G19" s="76"/>
+    </row>
+    <row r="20" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27">
         <v>2</v>
       </c>
-      <c r="C20" s="69" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" s="70"/>
-      <c r="E20" s="70"/>
-      <c r="F20" s="71"/>
-    </row>
-    <row r="21" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26">
+      <c r="C20" s="160" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="161"/>
+      <c r="E20" s="161"/>
+      <c r="F20" s="162"/>
+      <c r="G20" s="74" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
         <v>3</v>
       </c>
-      <c r="C21" s="161" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" s="162"/>
-      <c r="E21" s="162"/>
-      <c r="F21" s="163"/>
-    </row>
-    <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26">
+      <c r="C21" s="167" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="168"/>
+      <c r="E21" s="168"/>
+      <c r="F21" s="169"/>
+      <c r="G21" s="74" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="26"/>
+      <c r="B22" s="27">
         <v>4</v>
       </c>
-      <c r="C22" s="152"/>
-      <c r="D22" s="153"/>
-      <c r="E22" s="153"/>
-      <c r="F22" s="154"/>
-    </row>
-    <row r="23" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="33"/>
-      <c r="B23" s="29">
+      <c r="C22" s="180"/>
+      <c r="D22" s="181"/>
+      <c r="E22" s="181"/>
+      <c r="F22" s="182"/>
+      <c r="G22" s="28"/>
+    </row>
+    <row r="23" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="35"/>
+      <c r="B23" s="31">
         <v>6</v>
       </c>
-      <c r="C23" s="155" t="s">
-        <v>86</v>
-      </c>
-      <c r="D23" s="156"/>
-      <c r="E23" s="156"/>
-      <c r="F23" s="157"/>
-    </row>
-    <row r="24" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="31">
+      <c r="C23" s="186" t="s">
+        <v>115</v>
+      </c>
+      <c r="D23" s="187"/>
+      <c r="E23" s="187"/>
+      <c r="F23" s="188"/>
+      <c r="G23" s="79" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="33">
         <v>1</v>
       </c>
-      <c r="C24" s="109" t="s">
-        <v>91</v>
-      </c>
-      <c r="D24" s="110"/>
-      <c r="E24" s="110"/>
-      <c r="F24" s="111"/>
-    </row>
-    <row r="25" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26">
+      <c r="C24" s="123" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24" s="124"/>
+      <c r="E24" s="124"/>
+      <c r="F24" s="125"/>
+      <c r="G24" s="76" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27">
         <v>2</v>
       </c>
-      <c r="C25" s="161" t="s">
-        <v>89</v>
-      </c>
-      <c r="D25" s="162"/>
-      <c r="E25" s="162"/>
-      <c r="F25" s="163"/>
-    </row>
-    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26">
+      <c r="C25" s="167" t="s">
+        <v>120</v>
+      </c>
+      <c r="D25" s="168"/>
+      <c r="E25" s="168"/>
+      <c r="F25" s="169"/>
+      <c r="G25" s="74" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="26"/>
+      <c r="B26" s="27">
         <v>3</v>
       </c>
-      <c r="C26" s="146" t="s">
-        <v>108</v>
-      </c>
-      <c r="D26" s="147"/>
-      <c r="E26" s="147"/>
-      <c r="F26" s="148"/>
-    </row>
-    <row r="27" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="33"/>
-      <c r="B27" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="180" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" s="181"/>
-      <c r="E27" s="181"/>
-      <c r="F27" s="182"/>
-    </row>
-    <row r="28" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="31">
+      <c r="C26" s="170" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" s="171"/>
+      <c r="E26" s="171"/>
+      <c r="F26" s="172"/>
+      <c r="G26" s="74" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="35"/>
+      <c r="B27" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="183" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="184"/>
+      <c r="E27" s="184"/>
+      <c r="F27" s="185"/>
+      <c r="G27" s="47"/>
+    </row>
+    <row r="28" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="33">
         <v>2</v>
       </c>
-      <c r="C28" s="158"/>
-      <c r="D28" s="159"/>
-      <c r="E28" s="159"/>
-      <c r="F28" s="160"/>
-    </row>
-    <row r="29" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="34"/>
-      <c r="B29" s="24">
+      <c r="C28" s="189"/>
+      <c r="D28" s="190"/>
+      <c r="E28" s="190"/>
+      <c r="F28" s="191"/>
+      <c r="G28" s="76"/>
+    </row>
+    <row r="29" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="36"/>
+      <c r="B29" s="25">
         <v>4</v>
       </c>
-      <c r="C29" s="130" t="s">
-        <v>112</v>
-      </c>
-      <c r="D29" s="131"/>
-      <c r="E29" s="131"/>
-      <c r="F29" s="132"/>
-    </row>
-    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="34"/>
-      <c r="B30" s="26">
+      <c r="C29" s="102" t="s">
+        <v>152</v>
+      </c>
+      <c r="D29" s="103"/>
+      <c r="E29" s="103"/>
+      <c r="F29" s="104"/>
+      <c r="G29" s="84" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="36"/>
+      <c r="B30" s="27">
         <v>5</v>
       </c>
-      <c r="C30" s="130" t="s">
-        <v>115</v>
-      </c>
-      <c r="D30" s="131"/>
-      <c r="E30" s="131"/>
-      <c r="F30" s="132"/>
-    </row>
-    <row r="31" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="36"/>
-      <c r="B31" s="29">
+      <c r="C30" s="102" t="s">
+        <v>155</v>
+      </c>
+      <c r="D30" s="103"/>
+      <c r="E30" s="103"/>
+      <c r="F30" s="104"/>
+      <c r="G30" s="84" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="38"/>
+      <c r="B31" s="31">
         <v>6</v>
       </c>
       <c r="C31" s="177" t="s">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="D31" s="178"/>
       <c r="E31" s="178"/>
       <c r="F31" s="179"/>
-    </row>
-    <row r="32" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="B32" s="31">
+      <c r="G31" s="79" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="33">
         <v>1</v>
       </c>
-      <c r="C32" s="145" t="s">
-        <v>37</v>
-      </c>
-      <c r="D32" s="115"/>
-      <c r="E32" s="115"/>
-      <c r="F32" s="116"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="34"/>
-      <c r="B33" s="26">
+      <c r="C32" s="176" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" s="129"/>
+      <c r="E32" s="129"/>
+      <c r="F32" s="130"/>
+      <c r="G32" s="74" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="36"/>
+      <c r="B33" s="27">
         <v>2</v>
       </c>
-      <c r="C33" s="100" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" s="101"/>
-      <c r="E33" s="101"/>
-      <c r="F33" s="102"/>
-    </row>
-    <row r="34" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="35"/>
-      <c r="B34" s="27">
+      <c r="C33" s="114" t="s">
+        <v>51</v>
+      </c>
+      <c r="D33" s="115"/>
+      <c r="E33" s="115"/>
+      <c r="F33" s="116"/>
+      <c r="G33" s="77" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="37"/>
+      <c r="B34" s="29">
         <v>3</v>
       </c>
-      <c r="C34" s="100" t="s">
-        <v>88</v>
-      </c>
-      <c r="D34" s="101"/>
-      <c r="E34" s="101"/>
-      <c r="F34" s="102"/>
-    </row>
-    <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="35"/>
-      <c r="B35" s="27">
+      <c r="C34" s="114" t="s">
+        <v>119</v>
+      </c>
+      <c r="D34" s="115"/>
+      <c r="E34" s="115"/>
+      <c r="F34" s="116"/>
+      <c r="G34" s="77" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="37"/>
+      <c r="B35" s="29">
         <v>4</v>
       </c>
-      <c r="C35" s="161"/>
-      <c r="D35" s="162"/>
-      <c r="E35" s="162"/>
-      <c r="F35" s="163"/>
-    </row>
-    <row r="36" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="46"/>
-      <c r="B36" s="29">
+      <c r="C35" s="167"/>
+      <c r="D35" s="168"/>
+      <c r="E35" s="168"/>
+      <c r="F35" s="169"/>
+      <c r="G35" s="77"/>
+    </row>
+    <row r="36" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="50"/>
+      <c r="B36" s="31">
         <v>5</v>
       </c>
-      <c r="C36" s="152"/>
-      <c r="D36" s="153"/>
-      <c r="E36" s="153"/>
-      <c r="F36" s="154"/>
-    </row>
-    <row r="37" spans="1:6" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A37" s="47"/>
-      <c r="B37" s="48"/>
-      <c r="C37" s="174"/>
-      <c r="D37" s="175"/>
-      <c r="E37" s="175"/>
-      <c r="F37" s="176"/>
-    </row>
-    <row r="38" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="49"/>
-      <c r="B38" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="C38" s="171" t="s">
-        <v>83</v>
-      </c>
-      <c r="D38" s="172"/>
-      <c r="E38" s="172"/>
-      <c r="F38" s="173"/>
-    </row>
-    <row r="39" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="56" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="57"/>
-      <c r="C39" s="170" t="s">
-        <v>54</v>
-      </c>
-      <c r="D39" s="170"/>
-      <c r="E39" s="170"/>
-      <c r="F39" s="170"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C36" s="180"/>
+      <c r="D36" s="181"/>
+      <c r="E36" s="181"/>
+      <c r="F36" s="182"/>
+      <c r="G36" s="74"/>
+    </row>
+    <row r="37" spans="1:7" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="51"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="173"/>
+      <c r="D37" s="174"/>
+      <c r="E37" s="174"/>
+      <c r="F37" s="175"/>
+      <c r="G37" s="73"/>
+    </row>
+    <row r="38" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="53"/>
+      <c r="B38" s="54" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="164" t="s">
+        <v>112</v>
+      </c>
+      <c r="D38" s="165"/>
+      <c r="E38" s="165"/>
+      <c r="F38" s="166"/>
+      <c r="G38" s="82" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="64" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" s="65"/>
+      <c r="C39" s="163" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" s="163"/>
+      <c r="E39" s="163"/>
+      <c r="F39" s="163"/>
+      <c r="G39" s="63"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>117</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C21:F21"/>
     <mergeCell ref="C39:F39"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="C34:F34"/>
@@ -3207,24 +3588,6 @@
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C13:F13"/>
   </mergeCells>
   <conditionalFormatting sqref="C8">
     <cfRule type="expression" priority="1">
@@ -3247,7 +3610,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3256,10 +3619,11 @@
     <col min="4" max="4" width="16.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="18.42578125" style="2" customWidth="1"/>
     <col min="6" max="6" width="17.5703125" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -3267,15 +3631,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -3283,39 +3647,39 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -3325,35 +3689,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="203" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="213" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="203"/>
+      <c r="D7" s="213"/>
       <c r="E7" s="15" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="117" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" s="117"/>
-      <c r="E8" s="117"/>
-      <c r="F8" s="117"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="C8" s="131" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="131"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="131"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>0</v>
@@ -3364,361 +3728,457 @@
       <c r="D9" s="20"/>
       <c r="E9" s="21"/>
       <c r="F9" s="22"/>
-    </row>
-    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="24">
+      <c r="G9" s="23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="25">
         <v>3</v>
       </c>
-      <c r="C10" s="109" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" s="110"/>
-      <c r="E10" s="110"/>
-      <c r="F10" s="111"/>
-    </row>
-    <row r="11" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="25"/>
-      <c r="B11" s="26">
+      <c r="C10" s="123" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="124"/>
+      <c r="E10" s="124"/>
+      <c r="F10" s="125"/>
+      <c r="G10" s="76" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="26"/>
+      <c r="B11" s="27">
         <v>4</v>
       </c>
-      <c r="C11" s="204" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11" s="205"/>
-      <c r="E11" s="205"/>
-      <c r="F11" s="206"/>
-    </row>
-    <row r="12" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="C11" s="214" t="s">
+        <v>133</v>
+      </c>
+      <c r="D11" s="215"/>
+      <c r="E11" s="215"/>
+      <c r="F11" s="216"/>
+      <c r="G11" s="74" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
         <v>5</v>
       </c>
-      <c r="C12" s="204" t="s">
-        <v>98</v>
-      </c>
-      <c r="D12" s="205"/>
-      <c r="E12" s="205"/>
-      <c r="F12" s="206"/>
-    </row>
-    <row r="13" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="28"/>
-      <c r="B13" s="29">
+      <c r="C12" s="214" t="s">
+        <v>135</v>
+      </c>
+      <c r="D12" s="215"/>
+      <c r="E12" s="215"/>
+      <c r="F12" s="216"/>
+      <c r="G12" s="74" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="30"/>
+      <c r="B13" s="31">
         <v>6</v>
       </c>
-      <c r="C13" s="112"/>
-      <c r="D13" s="113"/>
-      <c r="E13" s="113"/>
-      <c r="F13" s="114"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A14" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="31">
+      <c r="C13" s="126"/>
+      <c r="D13" s="127"/>
+      <c r="E13" s="127"/>
+      <c r="F13" s="128"/>
+      <c r="G13" s="79"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="33">
         <v>1</v>
       </c>
-      <c r="C14" s="191"/>
-      <c r="D14" s="192"/>
-      <c r="E14" s="192"/>
-      <c r="F14" s="193"/>
-    </row>
-    <row r="15" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="25"/>
-      <c r="B15" s="26">
+      <c r="C14" s="223"/>
+      <c r="D14" s="224"/>
+      <c r="E14" s="224"/>
+      <c r="F14" s="225"/>
+      <c r="G14" s="45"/>
+    </row>
+    <row r="15" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="26"/>
+      <c r="B15" s="27">
         <v>2</v>
       </c>
-      <c r="C15" s="194"/>
-      <c r="D15" s="195"/>
-      <c r="E15" s="195" t="s">
-        <v>58</v>
-      </c>
-      <c r="F15" s="196"/>
-    </row>
-    <row r="16" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
+      <c r="C15" s="217"/>
+      <c r="D15" s="218"/>
+      <c r="E15" s="218" t="s">
+        <v>77</v>
+      </c>
+      <c r="F15" s="219"/>
+      <c r="G15" s="74" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
         <v>3</v>
       </c>
-      <c r="C16" s="100" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="101"/>
-      <c r="E16" s="101" t="s">
-        <v>61</v>
-      </c>
-      <c r="F16" s="102"/>
-    </row>
-    <row r="17" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
+      <c r="C16" s="114" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="115"/>
+      <c r="E16" s="115" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" s="116"/>
+      <c r="G16" s="74" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
         <v>4</v>
       </c>
-      <c r="C17" s="194" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17" s="195"/>
-      <c r="E17" s="195" t="s">
-        <v>121</v>
-      </c>
-      <c r="F17" s="196"/>
-    </row>
-    <row r="18" spans="1:6" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="33"/>
-      <c r="B18" s="29">
+      <c r="C17" s="217" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="218"/>
+      <c r="E17" s="218" t="s">
+        <v>163</v>
+      </c>
+      <c r="F17" s="219"/>
+      <c r="G17" s="74" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="35"/>
+      <c r="B18" s="31">
         <v>5</v>
       </c>
-      <c r="C18" s="94" t="s">
-        <v>122</v>
-      </c>
-      <c r="D18" s="200"/>
-      <c r="E18" s="201"/>
-      <c r="F18" s="202"/>
-    </row>
-    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="31">
+      <c r="C18" s="154" t="s">
+        <v>164</v>
+      </c>
+      <c r="D18" s="220"/>
+      <c r="E18" s="221"/>
+      <c r="F18" s="222"/>
+      <c r="G18" s="79" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="33">
         <v>1</v>
       </c>
-      <c r="C19" s="197"/>
-      <c r="D19" s="198"/>
-      <c r="E19" s="198"/>
-      <c r="F19" s="199"/>
-    </row>
-    <row r="20" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26">
+      <c r="C19" s="204"/>
+      <c r="D19" s="205"/>
+      <c r="E19" s="205"/>
+      <c r="F19" s="206"/>
+      <c r="G19" s="45"/>
+    </row>
+    <row r="20" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27">
         <v>2</v>
       </c>
-      <c r="C20" s="100" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" s="101"/>
-      <c r="E20" s="101" t="s">
-        <v>99</v>
-      </c>
-      <c r="F20" s="102"/>
-    </row>
-    <row r="21" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26">
+      <c r="C20" s="114" t="s">
+        <v>84</v>
+      </c>
+      <c r="D20" s="115"/>
+      <c r="E20" s="115" t="s">
+        <v>136</v>
+      </c>
+      <c r="F20" s="116"/>
+      <c r="G20" s="74" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
         <v>3</v>
       </c>
-      <c r="C21" s="100" t="s">
-        <v>100</v>
-      </c>
-      <c r="D21" s="101"/>
-      <c r="E21" s="101" t="s">
-        <v>64</v>
-      </c>
-      <c r="F21" s="102"/>
-    </row>
-    <row r="22" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="33"/>
-      <c r="B22" s="29">
+      <c r="C21" s="114" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21" s="115"/>
+      <c r="E21" s="115" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" s="116"/>
+      <c r="G21" s="74" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="35"/>
+      <c r="B22" s="31">
         <v>4</v>
       </c>
-      <c r="C22" s="94" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="95"/>
-      <c r="E22" s="95"/>
-      <c r="F22" s="96"/>
-    </row>
-    <row r="23" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="31">
+      <c r="C22" s="154" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="155"/>
+      <c r="E22" s="155"/>
+      <c r="F22" s="156"/>
+      <c r="G22" s="79" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="33">
         <v>1</v>
       </c>
-      <c r="C23" s="188"/>
-      <c r="D23" s="189"/>
-      <c r="E23" s="189"/>
-      <c r="F23" s="190"/>
-    </row>
-    <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26">
+      <c r="C23" s="226"/>
+      <c r="D23" s="227"/>
+      <c r="E23" s="227"/>
+      <c r="F23" s="228"/>
+      <c r="G23" s="45"/>
+    </row>
+    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27">
         <v>2</v>
       </c>
-      <c r="C24" s="142"/>
-      <c r="D24" s="143"/>
-      <c r="E24" s="143"/>
-      <c r="F24" s="144"/>
-    </row>
-    <row r="25" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26">
+      <c r="C24" s="198"/>
+      <c r="D24" s="199"/>
+      <c r="E24" s="199"/>
+      <c r="F24" s="200"/>
+      <c r="G24" s="74"/>
+    </row>
+    <row r="25" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27">
         <v>3</v>
       </c>
-      <c r="C25" s="130" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" s="131"/>
-      <c r="E25" s="131"/>
-      <c r="F25" s="132"/>
-    </row>
-    <row r="26" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="33"/>
-      <c r="B26" s="29">
+      <c r="C25" s="102" t="s">
+        <v>148</v>
+      </c>
+      <c r="D25" s="103"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="104"/>
+      <c r="G25" s="74" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="35"/>
+      <c r="B26" s="31">
         <v>4</v>
       </c>
-      <c r="C26" s="97" t="s">
-        <v>110</v>
-      </c>
-      <c r="D26" s="98"/>
-      <c r="E26" s="98"/>
-      <c r="F26" s="99"/>
-    </row>
-    <row r="27" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" s="31" t="s">
+      <c r="C26" s="157" t="s">
+        <v>149</v>
+      </c>
+      <c r="D26" s="158"/>
+      <c r="E26" s="158"/>
+      <c r="F26" s="159"/>
+      <c r="G26" s="74" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" s="176" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="129"/>
+      <c r="E27" s="129"/>
+      <c r="F27" s="130"/>
+      <c r="G27" s="45"/>
+    </row>
+    <row r="28" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="36"/>
+      <c r="B28" s="27">
+        <v>4</v>
+      </c>
+      <c r="C28" s="102" t="s">
+        <v>153</v>
+      </c>
+      <c r="D28" s="232"/>
+      <c r="E28" s="233"/>
+      <c r="F28" s="200"/>
+      <c r="G28" s="74" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="36"/>
+      <c r="B29" s="27">
+        <v>5</v>
+      </c>
+      <c r="C29" s="160"/>
+      <c r="D29" s="161"/>
+      <c r="E29" s="161" t="s">
+        <v>154</v>
+      </c>
+      <c r="F29" s="162"/>
+      <c r="G29" s="74" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="38"/>
+      <c r="B30" s="31">
+        <v>6</v>
+      </c>
+      <c r="C30" s="229"/>
+      <c r="D30" s="230"/>
+      <c r="E30" s="230"/>
+      <c r="F30" s="231"/>
+      <c r="G30" s="79"/>
+    </row>
+    <row r="31" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" s="25">
+        <v>1</v>
+      </c>
+      <c r="C31" s="204"/>
+      <c r="D31" s="205"/>
+      <c r="E31" s="205"/>
+      <c r="F31" s="206"/>
+      <c r="G31" s="84"/>
+    </row>
+    <row r="32" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="40"/>
+      <c r="B32" s="27">
+        <v>2</v>
+      </c>
+      <c r="C32" s="102" t="s">
+        <v>146</v>
+      </c>
+      <c r="D32" s="103"/>
+      <c r="E32" s="103"/>
+      <c r="F32" s="104"/>
+      <c r="G32" s="74" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="40"/>
+      <c r="B33" s="27">
+        <v>3</v>
+      </c>
+      <c r="C33" s="160" t="s">
+        <v>131</v>
+      </c>
+      <c r="D33" s="161"/>
+      <c r="E33" s="161"/>
+      <c r="F33" s="162"/>
+      <c r="G33" s="77" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="145" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" s="115"/>
-      <c r="E27" s="115"/>
-      <c r="F27" s="116"/>
-    </row>
-    <row r="28" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="34"/>
-      <c r="B28" s="26">
+    </row>
+    <row r="34" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="41"/>
+      <c r="B34" s="29">
         <v>4</v>
       </c>
-      <c r="C28" s="130" t="s">
-        <v>113</v>
-      </c>
-      <c r="D28" s="186"/>
-      <c r="E28" s="187"/>
-      <c r="F28" s="144"/>
-    </row>
-    <row r="29" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="34"/>
-      <c r="B29" s="26">
-        <v>5</v>
-      </c>
-      <c r="C29" s="69"/>
-      <c r="D29" s="70"/>
-      <c r="E29" s="70" t="s">
-        <v>114</v>
-      </c>
-      <c r="F29" s="71"/>
-    </row>
-    <row r="30" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="36"/>
-      <c r="B30" s="29">
-        <v>6</v>
-      </c>
-      <c r="C30" s="183"/>
-      <c r="D30" s="184"/>
-      <c r="E30" s="184"/>
-      <c r="F30" s="185"/>
-    </row>
-    <row r="31" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="B31" s="24">
-        <v>1</v>
-      </c>
-      <c r="C31" s="197"/>
-      <c r="D31" s="198"/>
-      <c r="E31" s="198"/>
-      <c r="F31" s="199"/>
-    </row>
-    <row r="32" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="38"/>
-      <c r="B32" s="26">
-        <v>2</v>
-      </c>
-      <c r="C32" s="130" t="s">
-        <v>107</v>
-      </c>
-      <c r="D32" s="131"/>
-      <c r="E32" s="131"/>
-      <c r="F32" s="132"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A33" s="38"/>
-      <c r="B33" s="26">
-        <v>3</v>
-      </c>
-      <c r="C33" s="69" t="s">
-        <v>96</v>
-      </c>
-      <c r="D33" s="70"/>
-      <c r="E33" s="70"/>
-      <c r="F33" s="71"/>
-    </row>
-    <row r="34" spans="1:6" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="39"/>
-      <c r="B34" s="27">
-        <v>4</v>
-      </c>
-      <c r="C34" s="124"/>
-      <c r="D34" s="125"/>
-      <c r="E34" s="125"/>
-      <c r="F34" s="126"/>
-    </row>
-    <row r="35" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="53"/>
-      <c r="B35" s="54"/>
+      <c r="C34" s="96"/>
+      <c r="D34" s="97"/>
+      <c r="E34" s="97"/>
+      <c r="F34" s="98"/>
+      <c r="G34" s="61"/>
+    </row>
+    <row r="35" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="57"/>
+      <c r="B35" s="58"/>
       <c r="C35" s="207"/>
       <c r="D35" s="208"/>
       <c r="E35" s="208"/>
       <c r="F35" s="209"/>
-    </row>
-    <row r="36" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="51"/>
-      <c r="B36" s="52" t="s">
-        <v>28</v>
+      <c r="G35" s="59"/>
+    </row>
+    <row r="36" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="55"/>
+      <c r="B36" s="56" t="s">
+        <v>29</v>
       </c>
       <c r="C36" s="210" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="D36" s="211"/>
       <c r="E36" s="211"/>
       <c r="F36" s="212"/>
-    </row>
-    <row r="37" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="56" t="s">
-        <v>47</v>
-      </c>
-      <c r="B37" s="57"/>
-      <c r="C37" s="170" t="s">
-        <v>48</v>
-      </c>
-      <c r="D37" s="170"/>
-      <c r="E37" s="170"/>
-      <c r="F37" s="170"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G36" s="85" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="64" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" s="65"/>
+      <c r="C37" s="163" t="s">
+        <v>62</v>
+      </c>
+      <c r="D37" s="163"/>
+      <c r="E37" s="163"/>
+      <c r="F37" s="163"/>
+      <c r="G37" s="63"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" s="2" t="s">
         <v>14</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>117</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C8:F8"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C37:F37"/>
@@ -3726,37 +4186,6 @@
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="C36:F36"/>
     <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
   </mergeCells>
   <conditionalFormatting sqref="C8">
     <cfRule type="expression" priority="1">
@@ -3779,7 +4208,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3787,80 +4216,81 @@
     <col min="3" max="3" width="19.5703125" style="2" customWidth="1"/>
     <col min="4" max="4" width="19.7109375" style="2" customWidth="1"/>
     <col min="5" max="6" width="18.85546875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="2"/>
-    <col min="8" max="8" width="9.42578125" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="2"/>
+    <col min="9" max="9" width="9.42578125" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A1" s="60" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A1" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="62" t="s">
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="71" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A2" s="60" t="s">
-        <v>65</v>
-      </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="62" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A2" s="69" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="71" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A3" s="60" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A3" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="62" t="s">
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="71" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
-      <c r="F4" s="63" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="F4" s="72" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="10">
@@ -3870,35 +4300,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="203" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="213" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="203"/>
+      <c r="D7" s="213"/>
       <c r="E7" s="15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="117" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" s="117"/>
-      <c r="E8" s="117"/>
-      <c r="F8" s="117"/>
-    </row>
-    <row r="9" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="C8" s="131" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="131"/>
+      <c r="E8" s="131"/>
+      <c r="F8" s="131"/>
+    </row>
+    <row r="9" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>0</v>
@@ -3909,278 +4339,328 @@
       <c r="D9" s="20"/>
       <c r="E9" s="21"/>
       <c r="F9" s="22"/>
-    </row>
-    <row r="10" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="24">
+      <c r="G9" s="23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="25">
         <v>2</v>
       </c>
-      <c r="C10" s="87"/>
-      <c r="D10" s="88"/>
-      <c r="E10" s="88"/>
-      <c r="F10" s="89"/>
-    </row>
-    <row r="11" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="25"/>
-      <c r="B11" s="26">
+      <c r="C10" s="147"/>
+      <c r="D10" s="148"/>
+      <c r="E10" s="148"/>
+      <c r="F10" s="149"/>
+      <c r="G10" s="76"/>
+    </row>
+    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="26"/>
+      <c r="B11" s="27">
         <v>3</v>
       </c>
-      <c r="C11" s="213"/>
-      <c r="D11" s="214"/>
-      <c r="E11" s="214"/>
-      <c r="F11" s="215"/>
-    </row>
-    <row r="12" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="C11" s="252"/>
+      <c r="D11" s="253"/>
+      <c r="E11" s="253"/>
+      <c r="F11" s="254"/>
+      <c r="G11" s="28"/>
+    </row>
+    <row r="12" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
         <v>4</v>
       </c>
-      <c r="C12" s="161" t="s">
-        <v>103</v>
-      </c>
-      <c r="D12" s="162"/>
-      <c r="E12" s="162"/>
-      <c r="F12" s="163"/>
-    </row>
-    <row r="13" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="55"/>
-      <c r="B13" s="27">
+      <c r="C12" s="167" t="s">
+        <v>141</v>
+      </c>
+      <c r="D12" s="168"/>
+      <c r="E12" s="168"/>
+      <c r="F12" s="169"/>
+      <c r="G12" s="74" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="60"/>
+      <c r="B13" s="29">
         <v>5</v>
       </c>
-      <c r="C13" s="161" t="s">
-        <v>106</v>
-      </c>
-      <c r="D13" s="162"/>
-      <c r="E13" s="162"/>
-      <c r="F13" s="163"/>
-    </row>
-    <row r="14" spans="1:8" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="28"/>
-      <c r="B14" s="29">
+      <c r="C13" s="167" t="s">
+        <v>144</v>
+      </c>
+      <c r="D13" s="168"/>
+      <c r="E13" s="168"/>
+      <c r="F13" s="169"/>
+      <c r="G13" s="77" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="30"/>
+      <c r="B14" s="31">
         <v>6</v>
       </c>
-      <c r="C14" s="94" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="95"/>
-      <c r="E14" s="95"/>
-      <c r="F14" s="96"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A15" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="31">
+      <c r="C14" s="154" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="155"/>
+      <c r="E14" s="155"/>
+      <c r="F14" s="156"/>
+      <c r="G14" s="79" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A15" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="33">
         <v>1</v>
       </c>
-      <c r="C15" s="191"/>
-      <c r="D15" s="192"/>
-      <c r="E15" s="192"/>
-      <c r="F15" s="193"/>
-    </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
+      <c r="C15" s="223"/>
+      <c r="D15" s="224"/>
+      <c r="E15" s="224"/>
+      <c r="F15" s="225"/>
+      <c r="G15" s="45"/>
+    </row>
+    <row r="16" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
         <v>2</v>
       </c>
-      <c r="C16" s="69" t="s">
-        <v>111</v>
-      </c>
-      <c r="D16" s="70"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="71"/>
-      <c r="H16" s="43"/>
-    </row>
-    <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
+      <c r="C16" s="160" t="s">
+        <v>151</v>
+      </c>
+      <c r="D16" s="161"/>
+      <c r="E16" s="161"/>
+      <c r="F16" s="162"/>
+      <c r="G16" s="74" t="s">
+        <v>75</v>
+      </c>
+      <c r="I16" s="46"/>
+    </row>
+    <row r="17" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
         <v>3</v>
       </c>
-      <c r="C17" s="69" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="71"/>
-    </row>
-    <row r="18" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="33"/>
-      <c r="B18" s="29">
+      <c r="C17" s="160" t="s">
+        <v>142</v>
+      </c>
+      <c r="D17" s="161"/>
+      <c r="E17" s="161"/>
+      <c r="F17" s="162"/>
+      <c r="G17" s="74" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="35"/>
+      <c r="B18" s="31">
         <v>4</v>
       </c>
-      <c r="C18" s="124"/>
-      <c r="D18" s="125"/>
-      <c r="E18" s="125"/>
-      <c r="F18" s="126"/>
-    </row>
-    <row r="19" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="31">
+      <c r="C18" s="96"/>
+      <c r="D18" s="97"/>
+      <c r="E18" s="97"/>
+      <c r="F18" s="98"/>
+      <c r="G18" s="47"/>
+    </row>
+    <row r="19" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="33">
         <v>4</v>
       </c>
-      <c r="C19" s="216" t="s">
-        <v>102</v>
-      </c>
-      <c r="D19" s="217"/>
-      <c r="E19" s="217"/>
-      <c r="F19" s="218"/>
-    </row>
-    <row r="20" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26">
+      <c r="C19" s="255" t="s">
+        <v>140</v>
+      </c>
+      <c r="D19" s="256"/>
+      <c r="E19" s="256"/>
+      <c r="F19" s="257"/>
+      <c r="G19" s="76" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27">
         <v>5</v>
       </c>
-      <c r="C20" s="161" t="s">
-        <v>119</v>
-      </c>
-      <c r="D20" s="162"/>
-      <c r="E20" s="162"/>
-      <c r="F20" s="163"/>
-    </row>
-    <row r="21" spans="1:6" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="33"/>
-      <c r="B21" s="29">
+      <c r="C20" s="167" t="s">
+        <v>159</v>
+      </c>
+      <c r="D20" s="168"/>
+      <c r="E20" s="168"/>
+      <c r="F20" s="169"/>
+      <c r="G20" s="74" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="35"/>
+      <c r="B21" s="31">
         <v>6</v>
       </c>
-      <c r="C21" s="94" t="s">
-        <v>120</v>
-      </c>
-      <c r="D21" s="95"/>
-      <c r="E21" s="95"/>
-      <c r="F21" s="96"/>
-    </row>
-    <row r="22" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="31">
+      <c r="C21" s="154" t="s">
+        <v>161</v>
+      </c>
+      <c r="D21" s="155"/>
+      <c r="E21" s="155"/>
+      <c r="F21" s="156"/>
+      <c r="G21" s="79" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="33">
         <v>1</v>
       </c>
-      <c r="C22" s="158"/>
-      <c r="D22" s="159"/>
-      <c r="E22" s="159"/>
-      <c r="F22" s="160"/>
-    </row>
-    <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="25"/>
-      <c r="B23" s="26">
+      <c r="C22" s="189"/>
+      <c r="D22" s="190"/>
+      <c r="E22" s="190"/>
+      <c r="F22" s="191"/>
+      <c r="G22" s="28"/>
+    </row>
+    <row r="23" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="26"/>
+      <c r="B23" s="27">
         <v>2</v>
       </c>
-      <c r="C23" s="152"/>
-      <c r="D23" s="153"/>
-      <c r="E23" s="153"/>
-      <c r="F23" s="154"/>
-    </row>
-    <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26">
+      <c r="C23" s="180"/>
+      <c r="D23" s="181"/>
+      <c r="E23" s="181"/>
+      <c r="F23" s="182"/>
+      <c r="G23" s="28"/>
+    </row>
+    <row r="24" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27">
         <v>3</v>
       </c>
-      <c r="C24" s="69" t="s">
-        <v>105</v>
-      </c>
-      <c r="D24" s="70"/>
-      <c r="E24" s="70"/>
-      <c r="F24" s="71"/>
-    </row>
-    <row r="25" spans="1:6" ht="17.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="33"/>
-      <c r="B25" s="29">
+      <c r="C24" s="160" t="s">
+        <v>143</v>
+      </c>
+      <c r="D24" s="161"/>
+      <c r="E24" s="161"/>
+      <c r="F24" s="162"/>
+      <c r="G24" s="74" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="17.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="35"/>
+      <c r="B25" s="31">
         <v>4</v>
       </c>
-      <c r="C25" s="97"/>
-      <c r="D25" s="98"/>
-      <c r="E25" s="98"/>
-      <c r="F25" s="99"/>
-    </row>
-    <row r="26" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="31">
+      <c r="C25" s="157"/>
+      <c r="D25" s="158"/>
+      <c r="E25" s="158"/>
+      <c r="F25" s="159"/>
+      <c r="G25" s="79"/>
+    </row>
+    <row r="26" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="33">
         <v>2</v>
       </c>
-      <c r="C26" s="228"/>
-      <c r="D26" s="229"/>
-      <c r="E26" s="229"/>
-      <c r="F26" s="230"/>
-    </row>
-    <row r="27" spans="1:6" ht="17.45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="34"/>
-      <c r="B27" s="24">
+      <c r="C26" s="243"/>
+      <c r="D26" s="244"/>
+      <c r="E26" s="244"/>
+      <c r="F26" s="245"/>
+      <c r="G26" s="74"/>
+    </row>
+    <row r="27" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="36"/>
+      <c r="B27" s="25">
         <v>3</v>
       </c>
-      <c r="C27" s="231" t="s">
-        <v>36</v>
-      </c>
-      <c r="D27" s="232"/>
-      <c r="E27" s="232"/>
-      <c r="F27" s="233"/>
-    </row>
-    <row r="28" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="34"/>
-      <c r="B28" s="26">
+      <c r="C27" s="246" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="247"/>
+      <c r="E27" s="247"/>
+      <c r="F27" s="248"/>
+      <c r="G27" s="74" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="36"/>
+      <c r="B28" s="27">
         <v>4</v>
       </c>
-      <c r="C28" s="130" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="131"/>
-      <c r="E28" s="131"/>
-      <c r="F28" s="132"/>
-    </row>
-    <row r="29" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="36"/>
-      <c r="B29" s="29">
+      <c r="C28" s="102" t="s">
+        <v>53</v>
+      </c>
+      <c r="D28" s="103"/>
+      <c r="E28" s="103"/>
+      <c r="F28" s="104"/>
+      <c r="G28" s="74" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="38"/>
+      <c r="B29" s="31">
         <v>5</v>
       </c>
-      <c r="C29" s="234"/>
-      <c r="D29" s="235"/>
-      <c r="E29" s="235"/>
-      <c r="F29" s="236"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="B30" s="24"/>
-      <c r="C30" s="222" t="s">
-        <v>59</v>
-      </c>
-      <c r="D30" s="223"/>
-      <c r="E30" s="223"/>
-      <c r="F30" s="224"/>
-    </row>
-    <row r="31" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="35"/>
-      <c r="B31" s="66"/>
-      <c r="C31" s="225"/>
-      <c r="D31" s="226"/>
-      <c r="E31" s="226"/>
-      <c r="F31" s="227"/>
-    </row>
-    <row r="32" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="67"/>
-      <c r="B32" s="68" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32" s="219" t="s">
-        <v>101</v>
-      </c>
-      <c r="D32" s="220"/>
-      <c r="E32" s="220"/>
-      <c r="F32" s="221"/>
+      <c r="C29" s="249"/>
+      <c r="D29" s="250"/>
+      <c r="E29" s="250"/>
+      <c r="F29" s="251"/>
+      <c r="G29" s="79"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="25"/>
+      <c r="C30" s="237" t="s">
+        <v>80</v>
+      </c>
+      <c r="D30" s="238"/>
+      <c r="E30" s="238"/>
+      <c r="F30" s="239"/>
+      <c r="G30" s="62"/>
+    </row>
+    <row r="31" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="37"/>
+      <c r="B31" s="86"/>
+      <c r="C31" s="240"/>
+      <c r="D31" s="241"/>
+      <c r="E31" s="241"/>
+      <c r="F31" s="242"/>
+      <c r="G31" s="89"/>
+    </row>
+    <row r="32" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="87"/>
+      <c r="B32" s="88" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="234" t="s">
+        <v>138</v>
+      </c>
+      <c r="D32" s="235"/>
+      <c r="E32" s="235"/>
+      <c r="F32" s="236"/>
+      <c r="G32" s="82" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
@@ -4188,24 +4668,11 @@
         <v>14</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>117</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C29:F29"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C10:F10"/>
@@ -4218,6 +4685,19 @@
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C24:F24"/>
   </mergeCells>
   <conditionalFormatting sqref="C8">
     <cfRule type="expression" priority="1">
